--- a/xlsx/Power/p21.xlsx
+++ b/xlsx/Power/p21.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C2D569-17E8-41BF-96FE-74636D184959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE39CB57-36F6-429D-B0B8-6046C7CF2AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1C994F9B-2AB3-4C20-9C9B-884BD957FB41}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1C994F9B-2AB3-4C20-9C9B-884BD957FB41}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.189</v>
       </c>
       <c r="C1">
-        <v>0.255</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="D1">
+        <v>0.18</v>
+      </c>
+      <c r="E1">
+        <v>0.26</v>
+      </c>
+      <c r="F1">
         <v>0.33</v>
       </c>
-      <c r="E1">
-        <v>0.377</v>
-      </c>
-      <c r="F1">
-        <v>0.434</v>
-      </c>
       <c r="G1">
-        <v>0.46400000000000002</v>
+        <v>0.37</v>
       </c>
       <c r="H1">
-        <v>0.52</v>
+        <v>0.441</v>
       </c>
       <c r="I1">
-        <v>0.57499999999999996</v>
+        <v>0.50900000000000001</v>
       </c>
       <c r="J1">
-        <v>0.56399999999999995</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.20699999999999999</v>
       </c>
       <c r="C2">
-        <v>0.28100000000000003</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="D2">
-        <v>0.36099999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="E2">
-        <v>0.41899999999999998</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="F2">
-        <v>0.46300000000000002</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="G2">
-        <v>0.50600000000000001</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="H2">
-        <v>0.56999999999999995</v>
+        <v>0.497</v>
       </c>
       <c r="I2">
-        <v>0.61599999999999999</v>
+        <v>0.55100000000000005</v>
       </c>
       <c r="J2">
-        <v>0.61599999999999999</v>
+        <v>0.54400000000000004</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>0.17799999999999999</v>
       </c>
       <c r="C3">
-        <v>0.20599999999999999</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="D3">
-        <v>0.26700000000000002</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="E3">
-        <v>0.28299999999999997</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="F3">
-        <v>0.32300000000000001</v>
+        <v>0.32600000000000001</v>
       </c>
       <c r="G3">
         <v>0.33600000000000002</v>
       </c>
       <c r="H3">
-        <v>0.373</v>
+        <v>0.375</v>
       </c>
       <c r="I3">
         <v>0.41499999999999998</v>
       </c>
       <c r="J3">
-        <v>0.40600000000000003</v>
+        <v>0.40899999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>8.7999999999999995E-2</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="B4">
-        <v>0.156</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="C4">
-        <v>0.184</v>
+        <v>0.186</v>
       </c>
       <c r="D4">
-        <v>0.224</v>
+        <v>0.219</v>
       </c>
       <c r="E4">
         <v>0.24199999999999999</v>
       </c>
       <c r="F4">
-        <v>0.26300000000000001</v>
+        <v>0.26600000000000001</v>
       </c>
       <c r="G4">
         <v>0.28799999999999998</v>
       </c>
       <c r="H4">
-        <v>0.307</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="I4">
         <v>0.35199999999999998</v>
       </c>
       <c r="J4">
-        <v>0.32300000000000001</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,28 +532,28 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="C5">
-        <v>5.7000000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>5.3999999999999999E-2</v>
+        <v>1E-3</v>
       </c>
       <c r="E5">
-        <v>5.0999999999999997E-2</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="F5">
-        <v>6.2E-2</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="G5">
-        <v>6.0999999999999999E-2</v>
+        <v>1.4E-2</v>
       </c>
       <c r="H5">
-        <v>5.3999999999999999E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="I5">
-        <v>5.6000000000000001E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="J5">
-        <v>6.2E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.22900000000000001</v>
       </c>
       <c r="C6">
-        <v>0.308</v>
+        <v>0.39300000000000002</v>
       </c>
       <c r="D6">
-        <v>0.372</v>
+        <v>0.40100000000000002</v>
       </c>
       <c r="E6">
-        <v>0.436</v>
+        <v>0.45200000000000001</v>
       </c>
       <c r="F6">
-        <v>0.49099999999999999</v>
+        <v>0.501</v>
       </c>
       <c r="G6">
-        <v>0.53200000000000003</v>
+        <v>0.53400000000000003</v>
       </c>
       <c r="H6">
-        <v>0.59399999999999997</v>
+        <v>0.59799999999999998</v>
       </c>
       <c r="I6">
-        <v>0.63900000000000001</v>
+        <v>0.64400000000000002</v>
       </c>
       <c r="J6">
-        <v>0.64400000000000002</v>
+        <v>0.65100000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,19 +596,19 @@
         <v>0.22500000000000001</v>
       </c>
       <c r="C7">
-        <v>0.28899999999999998</v>
+        <v>0.28399999999999997</v>
       </c>
       <c r="D7">
         <v>0.35</v>
       </c>
       <c r="E7">
-        <v>0.41499999999999998</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="F7">
-        <v>0.47699999999999998</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="G7">
-        <v>0.503</v>
+        <v>0.496</v>
       </c>
       <c r="H7">
         <v>0.56999999999999995</v>
@@ -617,7 +617,7 @@
         <v>0.62</v>
       </c>
       <c r="J7">
-        <v>0.61</v>
+        <v>0.60799999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.107</v>
       </c>
       <c r="C8">
-        <v>0.13700000000000001</v>
+        <v>0</v>
       </c>
       <c r="D8">
+        <v>0.03</v>
+      </c>
+      <c r="E8">
+        <v>0.08</v>
+      </c>
+      <c r="F8">
+        <v>0.106</v>
+      </c>
+      <c r="G8">
+        <v>0.153</v>
+      </c>
+      <c r="H8">
         <v>0.16700000000000001</v>
       </c>
-      <c r="E8">
-        <v>0.19700000000000001</v>
-      </c>
-      <c r="F8">
-        <v>0.216</v>
-      </c>
-      <c r="G8">
-        <v>0.23799999999999999</v>
-      </c>
-      <c r="H8">
-        <v>0.248</v>
-      </c>
       <c r="I8">
-        <v>0.30599999999999999</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="J8">
-        <v>0.28499999999999998</v>
+        <v>8.8999999999999996E-2</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="C9">
-        <v>0.19</v>
+        <v>0.432</v>
       </c>
       <c r="D9">
-        <v>0.10100000000000001</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="E9">
-        <v>8.8999999999999996E-2</v>
+        <v>0.51700000000000002</v>
       </c>
       <c r="F9">
-        <v>9.7000000000000003E-2</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="G9">
-        <v>9.4E-2</v>
+        <v>0.13</v>
       </c>
       <c r="H9">
-        <v>7.2999999999999995E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="I9">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="J9">
         <v>9.6000000000000002E-2</v>
-      </c>
-      <c r="J9">
-        <v>0.09</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p21.xlsx
+++ b/xlsx/Power/p21.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE39CB57-36F6-429D-B0B8-6046C7CF2AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90308316-DABD-48B5-B907-EBB621ABEA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1C994F9B-2AB3-4C20-9C9B-884BD957FB41}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1C994F9B-2AB3-4C20-9C9B-884BD957FB41}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.189</v>
       </c>
       <c r="C1">
-        <v>7.6999999999999999E-2</v>
+        <v>0.255</v>
       </c>
       <c r="D1">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="E1">
-        <v>0.26</v>
+        <v>0.377</v>
       </c>
       <c r="F1">
-        <v>0.33</v>
+        <v>0.434</v>
       </c>
       <c r="G1">
-        <v>0.37</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="H1">
-        <v>0.441</v>
+        <v>0.52</v>
       </c>
       <c r="I1">
-        <v>0.50900000000000001</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="J1">
-        <v>0.504</v>
+        <v>0.56399999999999995</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.20699999999999999</v>
       </c>
       <c r="C2">
-        <v>0.10199999999999999</v>
+        <v>0.28100000000000003</v>
       </c>
       <c r="D2">
-        <v>0.21</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="E2">
-        <v>0.29099999999999998</v>
+        <v>0.41899999999999998</v>
       </c>
       <c r="F2">
-        <v>0.36699999999999999</v>
+        <v>0.46300000000000002</v>
       </c>
       <c r="G2">
-        <v>0.41499999999999998</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="H2">
-        <v>0.497</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I2">
-        <v>0.55100000000000005</v>
+        <v>0.61599999999999999</v>
       </c>
       <c r="J2">
-        <v>0.54400000000000004</v>
+        <v>0.61599999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>0.17799999999999999</v>
       </c>
       <c r="C3">
-        <v>0.23300000000000001</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="D3">
-        <v>0.27400000000000002</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="E3">
-        <v>0.28799999999999998</v>
+        <v>0.28299999999999997</v>
       </c>
       <c r="F3">
-        <v>0.32600000000000001</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="G3">
         <v>0.33600000000000002</v>
       </c>
       <c r="H3">
-        <v>0.375</v>
+        <v>0.373</v>
       </c>
       <c r="I3">
         <v>0.41499999999999998</v>
       </c>
       <c r="J3">
-        <v>0.40899999999999997</v>
+        <v>0.40600000000000003</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>9.9000000000000005E-2</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="B4">
-        <v>0.16500000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="C4">
-        <v>0.186</v>
+        <v>0.184</v>
       </c>
       <c r="D4">
-        <v>0.219</v>
+        <v>0.223</v>
       </c>
       <c r="E4">
         <v>0.24199999999999999</v>
       </c>
       <c r="F4">
-        <v>0.26600000000000001</v>
+        <v>0.26300000000000001</v>
       </c>
       <c r="G4">
         <v>0.28799999999999998</v>
       </c>
       <c r="H4">
-        <v>0.30499999999999999</v>
+        <v>0.307</v>
       </c>
       <c r="I4">
         <v>0.35199999999999998</v>
       </c>
       <c r="J4">
-        <v>0.33</v>
+        <v>0.32300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,28 +532,28 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="D5">
-        <v>1E-3</v>
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="E5">
-        <v>6.0000000000000001E-3</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="F5">
-        <v>8.9999999999999993E-3</v>
+        <v>6.2E-2</v>
       </c>
       <c r="G5">
-        <v>1.4E-2</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="H5">
-        <v>1.6E-2</v>
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="I5">
-        <v>1.0999999999999999E-2</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="J5">
-        <v>1.7000000000000001E-2</v>
+        <v>6.2E-2</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.22900000000000001</v>
       </c>
       <c r="C6">
-        <v>0.39300000000000002</v>
+        <v>0.308</v>
       </c>
       <c r="D6">
-        <v>0.40100000000000002</v>
+        <v>0.372</v>
       </c>
       <c r="E6">
-        <v>0.45200000000000001</v>
+        <v>0.436</v>
       </c>
       <c r="F6">
-        <v>0.501</v>
+        <v>0.49099999999999999</v>
       </c>
       <c r="G6">
-        <v>0.53400000000000003</v>
+        <v>0.53200000000000003</v>
       </c>
       <c r="H6">
-        <v>0.59799999999999998</v>
+        <v>0.59399999999999997</v>
       </c>
       <c r="I6">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="J6">
         <v>0.64400000000000002</v>
-      </c>
-      <c r="J6">
-        <v>0.65100000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,19 +596,19 @@
         <v>0.22500000000000001</v>
       </c>
       <c r="C7">
-        <v>0.28399999999999997</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="D7">
         <v>0.35</v>
       </c>
       <c r="E7">
-        <v>0.41699999999999998</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="F7">
-        <v>0.47499999999999998</v>
+        <v>0.47699999999999998</v>
       </c>
       <c r="G7">
-        <v>0.496</v>
+        <v>0.503</v>
       </c>
       <c r="H7">
         <v>0.56999999999999995</v>
@@ -617,7 +617,7 @@
         <v>0.62</v>
       </c>
       <c r="J7">
-        <v>0.60799999999999998</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.107</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="D8">
-        <v>0.03</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="E8">
-        <v>0.08</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="F8">
-        <v>0.106</v>
+        <v>0.216</v>
       </c>
       <c r="G8">
-        <v>0.153</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="H8">
-        <v>0.16700000000000001</v>
+        <v>0.248</v>
       </c>
       <c r="I8">
-        <v>9.0999999999999998E-2</v>
+        <v>0.30599999999999999</v>
       </c>
       <c r="J8">
-        <v>8.8999999999999996E-2</v>
+        <v>0.28499999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="C9">
-        <v>0.432</v>
+        <v>0.19</v>
       </c>
       <c r="D9">
-        <v>0.82399999999999995</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="E9">
-        <v>0.51700000000000002</v>
+        <v>8.8999999999999996E-2</v>
       </c>
       <c r="F9">
-        <v>0.17599999999999999</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="G9">
-        <v>0.13</v>
+        <v>9.4E-2</v>
       </c>
       <c r="H9">
-        <v>9.5000000000000001E-2</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="I9">
-        <v>0.11799999999999999</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="J9">
-        <v>9.6000000000000002E-2</v>
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p21.xlsx
+++ b/xlsx/Power/p21.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90308316-DABD-48B5-B907-EBB621ABEA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE702993-D1AE-4549-AC7A-438F8EAF6F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1C994F9B-2AB3-4C20-9C9B-884BD957FB41}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1C994F9B-2AB3-4C20-9C9B-884BD957FB41}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -401,19 +401,19 @@
         <v>0.105</v>
       </c>
       <c r="B1">
-        <v>0.189</v>
+        <v>0.19</v>
       </c>
       <c r="C1">
         <v>0.255</v>
       </c>
       <c r="D1">
-        <v>0.33</v>
+        <v>0.33100000000000002</v>
       </c>
       <c r="E1">
-        <v>0.377</v>
+        <v>0.38100000000000001</v>
       </c>
       <c r="F1">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="G1">
         <v>0.46400000000000002</v>
@@ -422,10 +422,10 @@
         <v>0.52</v>
       </c>
       <c r="I1">
-        <v>0.57499999999999996</v>
+        <v>0.57799999999999996</v>
       </c>
       <c r="J1">
-        <v>0.56399999999999995</v>
+        <v>0.57299999999999995</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -433,7 +433,7 @@
         <v>0.115</v>
       </c>
       <c r="B2">
-        <v>0.20699999999999999</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="C2">
         <v>0.28100000000000003</v>
@@ -445,16 +445,16 @@
         <v>0.41899999999999998</v>
       </c>
       <c r="F2">
-        <v>0.46300000000000002</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="G2">
-        <v>0.50600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="H2">
-        <v>0.56999999999999995</v>
+        <v>0.56799999999999995</v>
       </c>
       <c r="I2">
-        <v>0.61599999999999999</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="J2">
         <v>0.61599999999999999</v>
@@ -465,100 +465,100 @@
         <v>0.1</v>
       </c>
       <c r="B3">
-        <v>0.17799999999999999</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="C3">
-        <v>0.20599999999999999</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="D3">
-        <v>0.26700000000000002</v>
+        <v>0.26800000000000002</v>
       </c>
       <c r="E3">
-        <v>0.28299999999999997</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="F3">
-        <v>0.32300000000000001</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="G3">
         <v>0.33600000000000002</v>
       </c>
       <c r="H3">
-        <v>0.373</v>
+        <v>0.378</v>
       </c>
       <c r="I3">
-        <v>0.41499999999999998</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="J3">
-        <v>0.40600000000000003</v>
+        <v>0.41399999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>8.7999999999999995E-2</v>
+        <v>8.5999999999999993E-2</v>
       </c>
       <c r="B4">
-        <v>0.156</v>
+        <v>0.161</v>
       </c>
       <c r="C4">
-        <v>0.184</v>
+        <v>0.185</v>
       </c>
       <c r="D4">
-        <v>0.223</v>
+        <v>0.22600000000000001</v>
       </c>
       <c r="E4">
-        <v>0.24199999999999999</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="F4">
-        <v>0.26300000000000001</v>
+        <v>0.26600000000000001</v>
       </c>
       <c r="G4">
-        <v>0.28799999999999998</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="H4">
-        <v>0.307</v>
+        <v>0.31</v>
       </c>
       <c r="I4">
-        <v>0.35199999999999998</v>
+        <v>0.35599999999999998</v>
       </c>
       <c r="J4">
-        <v>0.32300000000000001</v>
+        <v>0.33300000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>5.7000000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>3.5999999999999997E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="C5">
-        <v>5.7000000000000002E-2</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="D5">
-        <v>5.3999999999999999E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="E5">
-        <v>5.0999999999999997E-2</v>
+        <v>0.01</v>
       </c>
       <c r="F5">
-        <v>6.2E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G5">
-        <v>6.0999999999999999E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="H5">
-        <v>5.3999999999999999E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="I5">
-        <v>5.6000000000000001E-2</v>
+        <v>1.4E-2</v>
       </c>
       <c r="J5">
-        <v>6.2E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.128</v>
+        <v>0.127</v>
       </c>
       <c r="B6">
         <v>0.22900000000000001</v>
@@ -570,22 +570,22 @@
         <v>0.372</v>
       </c>
       <c r="E6">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="F6">
         <v>0.49099999999999999</v>
       </c>
       <c r="G6">
-        <v>0.53200000000000003</v>
+        <v>0.53</v>
       </c>
       <c r="H6">
         <v>0.59399999999999997</v>
       </c>
       <c r="I6">
-        <v>0.63900000000000001</v>
+        <v>0.63600000000000001</v>
       </c>
       <c r="J6">
-        <v>0.64400000000000002</v>
+        <v>0.64500000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -593,22 +593,22 @@
         <v>0.125</v>
       </c>
       <c r="B7">
-        <v>0.22500000000000001</v>
+        <v>0.224</v>
       </c>
       <c r="C7">
-        <v>0.28899999999999998</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="D7">
-        <v>0.35</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="E7">
         <v>0.41499999999999998</v>
       </c>
       <c r="F7">
-        <v>0.47699999999999998</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="G7">
-        <v>0.503</v>
+        <v>0.501</v>
       </c>
       <c r="H7">
         <v>0.56999999999999995</v>
@@ -631,13 +631,13 @@
         <v>0.13700000000000001</v>
       </c>
       <c r="D8">
-        <v>0.16700000000000001</v>
+        <v>0.16900000000000001</v>
       </c>
       <c r="E8">
-        <v>0.19700000000000001</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="F8">
-        <v>0.216</v>
+        <v>0.218</v>
       </c>
       <c r="G8">
         <v>0.23799999999999999</v>
@@ -646,7 +646,7 @@
         <v>0.248</v>
       </c>
       <c r="I8">
-        <v>0.30599999999999999</v>
+        <v>0.307</v>
       </c>
       <c r="J8">
         <v>0.28499999999999998</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>7.6999999999999999E-2</v>
+        <v>7.8E-2</v>
       </c>
       <c r="B9">
-        <v>9.1999999999999998E-2</v>
+        <v>9.4E-2</v>
       </c>
       <c r="C9">
         <v>0.19</v>
@@ -669,16 +669,16 @@
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="F9">
-        <v>9.7000000000000003E-2</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="G9">
         <v>9.4E-2</v>
       </c>
       <c r="H9">
-        <v>7.2999999999999995E-2</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="I9">
-        <v>9.6000000000000002E-2</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="J9">
         <v>0.09</v>
